--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,23 +33,11 @@
     <t>aggregate</t>
   </si>
   <si>
-    <t>聚集操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>clsMgr</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>集群管理、节点管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dataSync</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据同步：全量同步，正常增量数据同步</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -68,15 +56,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据修改操作：insert,update,delete,upsert
-lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>om</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>procedures</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,49 +68,164 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>查询操作：
+    <t>rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbMigrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理、节点管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步：全量同步，正常增量数据同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">数据修改操作：insert,update,delete,upsert
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lob</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>om补充异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">查询操作：
 query,count(Hint),index,cursor
-findandmodify,findandremove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbMigrate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>traction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务操作</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findandmodify,findandremove</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据切分（补充复杂场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>事务操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（补充全量同步异常场景）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG连接器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HADOOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动PYTHON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C、C++、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C#、PHP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,7 +233,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +248,52 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -163,7 +303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -186,21 +326,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -208,6 +397,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -219,7 +476,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -496,14 +753,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="27.125" customWidth="1"/>
+    <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,137 +768,253 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="11"/>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11"/>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="54">
+      <c r="A5" s="11"/>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="40.5">
+      <c r="A6" s="11"/>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="54">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="40.5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="40.5">
+      <c r="A9" s="11"/>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="11"/>
+      <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="11"/>
+      <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="40.5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="11"/>
+      <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="11"/>
+      <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2" t="s">
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="11"/>
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="11"/>
+      <c r="B18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="11"/>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="11"/>
+      <c r="B20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="12"/>
+      <c r="B23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A2:A23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -226,6 +226,10 @@
   </si>
   <si>
     <t>驱动C#、PHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -367,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -391,6 +395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
@@ -1010,6 +1015,11 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="13" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="1440" yWindow="-300" windowWidth="17715" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,26 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>胡晓均</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PG连接器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -230,6 +210,78 @@
   </si>
   <si>
     <t>配置参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳/黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳/余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳/龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷/龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷/黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳/余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳/黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净/龙阳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -386,6 +438,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -395,81 +448,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -481,7 +465,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -763,6 +747,7 @@
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -776,7 +761,7 @@
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -786,11 +771,11 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="11"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -798,11 +783,11 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="11"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -810,11 +795,11 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="54">
-      <c r="A5" s="11"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -822,11 +807,11 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="40.5">
-      <c r="A6" s="11"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
@@ -834,21 +819,21 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="11"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="11"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
@@ -856,11 +841,11 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="40.5">
-      <c r="A9" s="11"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
@@ -868,41 +853,41 @@
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="11"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="11"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="11"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
@@ -910,21 +895,21 @@
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="11"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="11"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
@@ -932,11 +917,11 @@
         <v>19</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="11"/>
+      <c r="A16" s="12"/>
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
@@ -944,82 +929,82 @@
         <v>27</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="11"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="11"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="11"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="11"/>
+      <c r="A20" s="12"/>
       <c r="B20" s="9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="12"/>
+      <c r="B21" s="9" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="11"/>
-      <c r="B21" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="11"/>
+      <c r="A22" s="12"/>
       <c r="B22" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12"/>
+      <c r="A23" s="13"/>
       <c r="B23" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="B24" s="13" t="s">
-        <v>40</v>
+      <c r="B24" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -11,12 +11,15 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$27</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="49">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,10 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>modifyOperation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>procedures</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -64,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>queryOpertion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,35 +103,234 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据同步：全量同步，正常增量数据同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">数据修改操作：insert,update,delete,upsert
-</t>
-    </r>
+    <t>om补充异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据切分（补充复杂场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="5" tint="-0.249977111117893"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>lob</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>om补充异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">查询操作：
-query,count(Hint),index,cursor
+      <t>事务操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（补充全量同步异常场景）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG连接器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HADOOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动PYTHON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C、C++、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C#、PHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据安全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据中心对外SSL加密传输</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库本地文件离线检测和修复工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>驱动JAVA、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Script</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">数据同步：全量同步，正常增量数据同步
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据中心灾备</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+  </si>
+  <si>
+    <t>余婷</t>
+  </si>
+  <si>
+    <t>王文净</t>
+  </si>
+  <si>
+    <t>龙阳</t>
+  </si>
+  <si>
+    <t>主要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>数据修改操作：insert,update,delete,upsert
+lob
+查询操作：
+query（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>读写分离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）,count(Hint),index（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>多索引及复合索引</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）,cursor,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据压缩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,数据一致性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -153,135 +347,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据切分（补充复杂场景）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>事务操作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（补充全量同步异常场景）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PG连接器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HIVE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HADOOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动PYTHON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动C、C++、</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动JAVA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动C#、PHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮/余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净/吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳/黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙阳/余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳/龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮/吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷/龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷/吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷/黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷/王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净/吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳/王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮/龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙阳/余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙阳/王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳/王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳/黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净/龙阳</t>
+    <t>基本操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -289,7 +355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +416,36 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -394,9 +490,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -407,23 +501,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -433,20 +523,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,15 +837,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -758,258 +852,435 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="11" t="s">
+      <c r="D1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="12"/>
+    <row r="3" spans="1:6">
+      <c r="A3" s="14"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27">
+      <c r="A4" s="14"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="54">
-      <c r="A5" s="12"/>
+      <c r="C4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54">
+      <c r="A5" s="14"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A6" s="14"/>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A7" s="14"/>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="108">
+      <c r="A8" s="14"/>
+      <c r="B8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="14"/>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="14"/>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A11" s="14"/>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="14"/>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="14"/>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="14"/>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="14"/>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="14"/>
+      <c r="B16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="14"/>
+      <c r="B17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="14"/>
+      <c r="B18" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="40.5">
-      <c r="A6" s="12"/>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="14"/>
+      <c r="B19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="14"/>
+      <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="6" t="s">
+      <c r="F20" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="14"/>
+      <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="14"/>
+      <c r="B22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="14"/>
+      <c r="B23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="F23" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="14"/>
+      <c r="B24" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="40.5">
-      <c r="A9" s="12"/>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="12"/>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="12"/>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="12"/>
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="12"/>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="12"/>
-      <c r="B17" s="9" t="s">
+      <c r="F24" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="14"/>
+      <c r="B25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="12"/>
-      <c r="B18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="12"/>
-      <c r="B19" s="9" t="s">
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="14"/>
+      <c r="B26" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="12"/>
-      <c r="B21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="C26" s="11"/>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="12"/>
-      <c r="B22" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="13"/>
-      <c r="B23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="10" t="s">
-        <v>35</v>
-      </c>
+    <row r="27" spans="1:6">
+      <c r="A27" s="14"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="11"/>
+      <c r="F27" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A23"/>
+    <mergeCell ref="A2:A27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,13 +48,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>元数据操作：
-domain,
-CS(create,drop,list),
-CL(create,drop,alter,list)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>procedures</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,10 +85,6 @@
   </si>
   <si>
     <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -192,23 +181,6 @@
   </si>
   <si>
     <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>驱动JAVA、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Java Script</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -350,12 +322,88 @@
     <t>基本操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.17完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.16完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作：
+domain,
+CS(create,drop,list),
+CL(create,drop,alter,list)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.10完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.12完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.15完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.14完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>驱动JAVA、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Script</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.19完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.11完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,6 +494,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -513,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -531,18 +586,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -837,14 +894,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,432 +911,483 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="18"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="27">
-      <c r="A4" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27">
+      <c r="A4" s="18"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="54">
-      <c r="A5" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54">
+      <c r="A5" s="18"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A6" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" hidden="1" customHeight="1">
+      <c r="A6" s="18"/>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="13.5" hidden="1" customHeight="1">
+      <c r="A7" s="18"/>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108">
+      <c r="A8" s="18"/>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="18"/>
+      <c r="B9" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="108">
-      <c r="A8" s="14"/>
-      <c r="B8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="14"/>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="18"/>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A11" s="14"/>
+        <v>41</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7" ht="13.5" hidden="1" customHeight="1">
+      <c r="A11" s="18"/>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="18"/>
       <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
+      <c r="A13" s="18"/>
+      <c r="B13" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="14"/>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="14"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="18"/>
       <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
+      <c r="A15" s="18"/>
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="14"/>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="14"/>
+    <row r="16" spans="1:7">
+      <c r="A16" s="18"/>
       <c r="B16" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="18"/>
       <c r="B17" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="18"/>
       <c r="B18" s="8" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
+      <c r="A19" s="18"/>
       <c r="B19" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
         <v>41</v>
       </c>
-      <c r="E19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="14"/>
+      <c r="F19" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="18"/>
       <c r="B20" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" hidden="1">
+      <c r="A21" s="18"/>
       <c r="B21" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="14"/>
+        <v>41</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1">
+      <c r="A22" s="18"/>
       <c r="B22" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="14"/>
+        <v>40</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
+      <c r="A23" s="18"/>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="F23" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="14"/>
+      <c r="F23" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="18"/>
       <c r="B24" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
+      <c r="A25" s="18"/>
+      <c r="B25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="14"/>
-      <c r="B25" s="12" t="s">
+    <row r="26" spans="1:7" hidden="1">
+      <c r="A26" s="18"/>
+      <c r="B26" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="14"/>
-      <c r="B26" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
+      <c r="A27" s="18"/>
       <c r="B27" s="12"/>
       <c r="C27" s="11"/>
       <c r="F27" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:F27">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="高"/>
+        <filter val="中"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:A27"/>
   </mergeCells>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="62">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -396,6 +396,10 @@
   </si>
   <si>
     <t>计划6.11完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM安装部署、web监控</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -592,20 +596,88 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -617,7 +689,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -894,7 +966,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -924,7 +995,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -942,12 +1013,12 @@
       <c r="F2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="18"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -968,7 +1039,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="18"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -989,7 +1060,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="54">
-      <c r="A5" s="18"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1009,12 +1080,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.5" hidden="1" customHeight="1">
-      <c r="A6" s="18"/>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A6" s="20"/>
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="D6" t="s">
         <v>36</v>
       </c>
@@ -1025,8 +1098,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.5" hidden="1" customHeight="1">
-      <c r="A7" s="18"/>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A7" s="20"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1044,7 +1117,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="108">
-      <c r="A8" s="18"/>
+      <c r="A8" s="20"/>
       <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
@@ -1065,7 +1138,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="18"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1079,12 +1152,12 @@
       <c r="F9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="18"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1095,13 +1168,13 @@
       <c r="E10" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="19"/>
-    </row>
-    <row r="11" spans="1:7" ht="13.5" hidden="1" customHeight="1">
-      <c r="A11" s="18"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A11" s="20"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1117,7 +1190,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="18"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1137,8 +1210,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
-      <c r="A13" s="18"/>
+    <row r="13" spans="1:7">
+      <c r="A13" s="20"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1154,7 +1227,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="18"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1174,8 +1247,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
-      <c r="A15" s="18"/>
+    <row r="15" spans="1:7">
+      <c r="A15" s="20"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1193,7 +1266,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="18"/>
+      <c r="A16" s="20"/>
       <c r="B16" s="8" t="s">
         <v>25</v>
       </c>
@@ -1212,7 +1285,7 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="18"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
@@ -1231,7 +1304,7 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="18"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="8" t="s">
         <v>58</v>
       </c>
@@ -1249,8 +1322,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
-      <c r="A19" s="18"/>
+    <row r="19" spans="1:7">
+      <c r="A19" s="20"/>
       <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
@@ -1266,7 +1339,7 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="18"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="8" t="s">
         <v>21</v>
       </c>
@@ -1284,8 +1357,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
-      <c r="A21" s="18"/>
+    <row r="21" spans="1:7">
+      <c r="A21" s="20"/>
       <c r="B21" s="8" t="s">
         <v>22</v>
       </c>
@@ -1300,8 +1373,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
-      <c r="A22" s="18"/>
+    <row r="22" spans="1:7">
+      <c r="A22" s="20"/>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
@@ -1316,8 +1389,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
-      <c r="A23" s="18"/>
+    <row r="23" spans="1:7">
+      <c r="A23" s="20"/>
       <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
@@ -1327,7 +1400,7 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="18"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="10" t="s">
         <v>28</v>
       </c>
@@ -1345,8 +1418,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
-      <c r="A25" s="18"/>
+    <row r="25" spans="1:7">
+      <c r="A25" s="20"/>
       <c r="B25" s="12" t="s">
         <v>29</v>
       </c>
@@ -1360,8 +1433,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
-      <c r="A26" s="18"/>
+    <row r="26" spans="1:7">
+      <c r="A26" s="20"/>
       <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
@@ -1373,20 +1446,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="18"/>
+    <row r="27" spans="1:7">
+      <c r="A27" s="20"/>
       <c r="B27" s="12"/>
       <c r="C27" s="11"/>
       <c r="F27" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F27">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="高"/>
-        <filter val="中"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:A27"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="70">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,6 +187,102 @@
     <t>吴艳</t>
   </si>
   <si>
+    <t>黄晓妮</t>
+  </si>
+  <si>
+    <t>余婷</t>
+  </si>
+  <si>
+    <t>王文净</t>
+  </si>
+  <si>
+    <t>龙阳</t>
+  </si>
+  <si>
+    <t>主要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.17完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.16完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作：
+domain,
+CS(create,drop,list),
+CL(create,drop,alter,list)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.10完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.12完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.15完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.14完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>驱动JAVA、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Script</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.19完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.11完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM安装部署、web监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">数据同步：全量同步，正常增量数据同步
 </t>
@@ -205,29 +301,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>黄晓妮</t>
-  </si>
-  <si>
-    <t>余婷</t>
-  </si>
-  <si>
-    <t>王文净</t>
-  </si>
-  <si>
-    <t>龙阳</t>
-  </si>
-  <si>
-    <t>主要责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次要责任人</t>
+    <t>完成时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定用户场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">黄晓妮（余婷） </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮（龙阳）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>数据修改操作：insert,update,delete,upsert
-lob
+lob，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findandmodify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 查询操作：
 query（</t>
     </r>
@@ -294,112 +411,26 @@
       </rPr>
       <t>,数据一致性</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>findandmodify,findandremove</t>
-    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.12完成测试方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成测试设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.17完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.16完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据操作：
-domain,
-CS(create,drop,list),
-CL(create,drop,alter,list)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.10完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.12完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.15完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.14完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>驱动JAVA、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Java Script</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.19完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.11完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM安装部署、web监控</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -598,6 +629,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -966,14 +998,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="3" width="33.875" customWidth="1"/>
+    <col min="7" max="8" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,43 +1016,46 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="20"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="21"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1029,25 +1066,25 @@
         <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="20"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="40.5">
+      <c r="A4" s="21"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -1056,50 +1093,50 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="54">
-      <c r="A5" s="20"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="54">
+      <c r="A5" s="21"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="20"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.5" hidden="1" customHeight="1">
+      <c r="A6" s="21"/>
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="20"/>
+    <row r="7" spans="1:8" ht="13.5" hidden="1" customHeight="1">
+      <c r="A7" s="21"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1107,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -1116,71 +1153,71 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="108">
-      <c r="A8" s="20"/>
+    <row r="8" spans="1:8" ht="108">
+      <c r="A8" s="21"/>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="20"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="21"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="20"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1">
+      <c r="A10" s="21"/>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>56</v>
-      </c>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="20"/>
+    <row r="11" spans="1:8" ht="13.5" hidden="1" customHeight="1">
+      <c r="A11" s="21"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -1189,8 +1226,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="20"/>
+    <row r="12" spans="1:8">
+      <c r="A12" s="21"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1201,33 +1238,33 @@
         <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1">
+      <c r="A13" s="21"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="20"/>
+    <row r="14" spans="1:8">
+      <c r="A14" s="21"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1235,20 +1272,20 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
         <v>38</v>
-      </c>
-      <c r="E14" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="20"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1">
+      <c r="A15" s="21"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1256,96 +1293,96 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="20"/>
+    <row r="16" spans="1:8">
+      <c r="A16" s="21"/>
       <c r="B16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" t="s">
+      <c r="D16" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
         <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="20"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="21"/>
       <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="20"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="21"/>
       <c r="B18" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="20"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" hidden="1">
+      <c r="A19" s="21"/>
       <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="20"/>
+    <row r="20" spans="1:8">
+      <c r="A20" s="21"/>
       <c r="B20" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
@@ -1354,43 +1391,46 @@
         <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="20"/>
+        <v>55</v>
+      </c>
+      <c r="H20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1">
+      <c r="A21" s="21"/>
       <c r="B21" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
         <v>40</v>
-      </c>
-      <c r="E21" t="s">
-        <v>41</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="20"/>
+    <row r="22" spans="1:8" hidden="1">
+      <c r="A22" s="21"/>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="20"/>
+    <row r="23" spans="1:8" hidden="1">
+      <c r="A23" s="21"/>
       <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
@@ -1399,27 +1439,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="20"/>
+    <row r="24" spans="1:8">
+      <c r="A24" s="21"/>
       <c r="B24" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="20"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1">
+      <c r="A25" s="21"/>
       <c r="B25" s="12" t="s">
         <v>29</v>
       </c>
@@ -1433,28 +1473,34 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="20"/>
+    <row r="26" spans="1:8" hidden="1">
+      <c r="A26" s="21"/>
       <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="20"/>
+    <row r="27" spans="1:8" hidden="1">
+      <c r="A27" s="21"/>
       <c r="B27" s="12"/>
       <c r="C27" s="11"/>
       <c r="F27" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F27">
-    <filterColumn colId="5"/>
+    <filterColumn colId="3"/>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="高"/>
+        <filter val="中"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:A27"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,102 +187,6 @@
     <t>吴艳</t>
   </si>
   <si>
-    <t>黄晓妮</t>
-  </si>
-  <si>
-    <t>余婷</t>
-  </si>
-  <si>
-    <t>王文净</t>
-  </si>
-  <si>
-    <t>龙阳</t>
-  </si>
-  <si>
-    <t>主要责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次要责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成测试设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.17完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.16完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据操作：
-domain,
-CS(create,drop,list),
-CL(create,drop,alter,list)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.10完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.12完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.15完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.14完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>驱动JAVA、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Java Script</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.19完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.11完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM安装部署、web监控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">数据同步：全量同步，正常增量数据同步
 </t>
@@ -301,50 +205,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风险</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不确定用户场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">黄晓妮（余婷） </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮（龙阳）</t>
+    <t>黄晓妮</t>
+  </si>
+  <si>
+    <t>余婷</t>
+  </si>
+  <si>
+    <t>王文净</t>
+  </si>
+  <si>
+    <t>龙阳</t>
+  </si>
+  <si>
+    <t>主要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次要责任人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>数据修改操作：insert,update,delete,upsert
-lob，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>findandmodify</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+lob
 查询操作：
 query（</t>
     </r>
@@ -411,6 +294,59 @@
       </rPr>
       <t>,数据一致性</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findandmodify,findandremove</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.17完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.16完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作：
+domain,
+CS(create,drop,list),
+CL(create,drop,alter,list)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -418,11 +354,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
+    <t>计划6.10完成测试方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -430,7 +362,48 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基本操作</t>
+    <t>计划6.15完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.14完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>驱动JAVA、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Script</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.19完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.11完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM安装部署、web监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -603,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -629,7 +602,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -998,16 +970,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="3" width="33.875" customWidth="1"/>
-    <col min="7" max="8" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1016,46 +986,43 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="21"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="20"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1066,25 +1033,25 @@
         <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="40.5">
-      <c r="A4" s="21"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27">
+      <c r="A4" s="20"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -1093,50 +1060,50 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="54">
-      <c r="A5" s="21"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54">
+      <c r="A5" s="20"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A6" s="21"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A6" s="20"/>
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A7" s="21"/>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A7" s="20"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1144,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -1153,71 +1120,71 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="108">
-      <c r="A8" s="21"/>
+    <row r="8" spans="1:7" ht="108">
+      <c r="A8" s="20"/>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="21"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="20"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1">
-      <c r="A10" s="21"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="20"/>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A11" s="21"/>
+    <row r="11" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A11" s="20"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -1226,8 +1193,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="21"/>
+    <row r="12" spans="1:7">
+      <c r="A12" s="20"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1238,33 +1205,33 @@
         <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1">
-      <c r="A13" s="21"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="20"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="21"/>
+    <row r="14" spans="1:7">
+      <c r="A14" s="20"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1272,20 +1239,20 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1">
-      <c r="A15" s="21"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="20"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1293,96 +1260,96 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="21"/>
+    <row r="16" spans="1:7">
+      <c r="A16" s="20"/>
       <c r="B16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="19" t="s">
-        <v>62</v>
+      <c r="D16" t="s">
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="21"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="20"/>
       <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="21"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="20"/>
       <c r="B18" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1">
-      <c r="A19" s="21"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="20"/>
       <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="21"/>
+    <row r="20" spans="1:7">
+      <c r="A20" s="20"/>
       <c r="B20" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
@@ -1391,46 +1358,43 @@
         <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1">
-      <c r="A21" s="21"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="20"/>
       <c r="B21" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1">
-      <c r="A22" s="21"/>
+    <row r="22" spans="1:7">
+      <c r="A22" s="20"/>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
         <v>40</v>
-      </c>
-      <c r="E22" t="s">
-        <v>39</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1">
-      <c r="A23" s="21"/>
+    <row r="23" spans="1:7">
+      <c r="A23" s="20"/>
       <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
@@ -1439,27 +1403,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="21"/>
+    <row r="24" spans="1:7">
+      <c r="A24" s="20"/>
       <c r="B24" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1">
-      <c r="A25" s="21"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="20"/>
       <c r="B25" s="12" t="s">
         <v>29</v>
       </c>
@@ -1473,35 +1437,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1">
-      <c r="A26" s="21"/>
+    <row r="26" spans="1:7">
+      <c r="A26" s="20"/>
       <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1">
-      <c r="A27" s="21"/>
+    <row r="27" spans="1:7">
+      <c r="A27" s="20"/>
       <c r="B27" s="12"/>
       <c r="C27" s="11"/>
       <c r="F27" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F27">
-    <filterColumn colId="3"/>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="高"/>
-        <filter val="中"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G27"/>
   <mergeCells count="1">
     <mergeCell ref="A2:A27"/>
   </mergeCells>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,10 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PG连接器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HIVE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -222,6 +218,106 @@
   </si>
   <si>
     <t>次要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.17完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.16完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作：
+domain,
+CS(create,drop,list),
+CL(create,drop,alter,list)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.10完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.12完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.15完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.14完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>驱动JAVA、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Script</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.19完成测试方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划6.11完成测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM安装部署、web监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG连接器、修改后的PG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RocketsDB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kettle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -319,91 +415,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成测试设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.17完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.16完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据操作：
-domain,
-CS(create,drop,list),
-CL(create,drop,alter,list)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.10完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.12完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.15完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.14完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>驱动JAVA、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Java Script</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.19完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.11完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM安装部署、web监控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
+    <t>sdbimprt导入导出工具</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,12 +522,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -576,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -586,7 +616,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -608,80 +637,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -693,7 +660,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -970,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
@@ -985,44 +952,44 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>47</v>
+        <v>31</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1030,171 +997,171 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="20"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>37</v>
+      <c r="C4" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54">
-      <c r="A5" s="20"/>
+      <c r="A5" s="19"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="20"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="20"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108">
+      <c r="A8" s="19"/>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="108">
-      <c r="A8" s="20"/>
-      <c r="B8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="20"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="20"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="14" t="s">
         <v>35</v>
       </c>
+      <c r="F11" s="13" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="20"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1202,259 +1169,271 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="20"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
         <v>38</v>
       </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="20"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="20"/>
-      <c r="B16" s="8" t="s">
-        <v>25</v>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
       <c r="F16" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="20"/>
-      <c r="B17" s="8" t="s">
-        <v>24</v>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="20"/>
-      <c r="B18" s="8" t="s">
-        <v>58</v>
+      <c r="A18" s="19"/>
+      <c r="B18" s="24" t="s">
+        <v>56</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="20"/>
-      <c r="B19" s="8" t="s">
-        <v>26</v>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="20"/>
-      <c r="B20" s="8" t="s">
-        <v>21</v>
+      <c r="A20" s="19"/>
+      <c r="B20" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="20"/>
-      <c r="B21" s="8" t="s">
-        <v>22</v>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
         <v>40</v>
       </c>
-      <c r="E21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>35</v>
+      <c r="F21" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="20"/>
-      <c r="B22" s="8" t="s">
-        <v>23</v>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="19"/>
+      <c r="B23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="F23" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="19"/>
+      <c r="B24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="19"/>
+      <c r="B25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="20"/>
-      <c r="B23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="F23" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="20"/>
-      <c r="B24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="20"/>
-      <c r="B25" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="11" t="s">
+      <c r="F25" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="19"/>
+      <c r="B26" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="20"/>
-      <c r="B26" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="11"/>
+      <c r="C26" s="10"/>
       <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="20"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="11"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="10"/>
       <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G27"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,10 +140,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>驱动C#、PHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>配置参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -273,23 +269,6 @@
   </si>
   <si>
     <t>计划6.14完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>驱动JAVA、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Java Script</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -416,6 +395,42 @@
   </si>
   <si>
     <t>sdbimprt导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Java Script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C#</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -631,18 +646,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
@@ -953,43 +969,43 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="19"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -997,171 +1013,171 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="19"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54">
-      <c r="A5" s="19"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="19"/>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="19" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108">
+      <c r="A8" s="25"/>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="108">
-      <c r="A8" s="19"/>
-      <c r="B8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="19"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="18" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="19"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1169,36 +1185,36 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="19"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1206,20 +1222,20 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
       </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="19"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1227,218 +1243,246 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="19"/>
-      <c r="B18" s="24" t="s">
-        <v>56</v>
+      <c r="A18" s="25"/>
+      <c r="B18" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20" t="s">
-        <v>25</v>
+      <c r="A19" s="25"/>
+      <c r="B19" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>34</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="19"/>
-      <c r="B20" s="24" t="s">
-        <v>61</v>
+      <c r="A20" s="25"/>
+      <c r="B20" s="18" t="s">
+        <v>72</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G20" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
-        <v>21</v>
+      <c r="A21" s="25"/>
+      <c r="B21" s="18" t="s">
+        <v>71</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>34</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20" t="s">
-        <v>22</v>
+      <c r="A22" s="25"/>
+      <c r="B22" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="25"/>
+      <c r="B23" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="19"/>
-      <c r="B23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="F23" s="14" t="s">
-        <v>34</v>
+      <c r="F23" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="19"/>
-      <c r="B24" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="10"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s">
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>58</v>
+        <v>38</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="19"/>
-      <c r="B25" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>34</v>
+      <c r="A25" s="25"/>
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="F25" s="14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="19"/>
-      <c r="B26" s="22" t="s">
-        <v>30</v>
+      <c r="A26" s="25"/>
+      <c r="B26" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="25"/>
+      <c r="B27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="19"/>
-      <c r="B27" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="F27" s="4"/>
+      <c r="F27" s="13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="25"/>
+      <c r="B29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G29"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:A27"/>
+    <mergeCell ref="A2:A29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdbMigrate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>split</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,10 +85,6 @@
   </si>
   <si>
     <t>集群管理、节点管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>om补充异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -136,14 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>驱动C、C++、</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>权限管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,10 +149,6 @@
   </si>
   <si>
     <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -264,10 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>计划6.14完成测试方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -277,10 +253,6 @@
   </si>
   <si>
     <t>计划6.11完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM安装部署、web监控</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -394,14 +366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdbimprt导入导出工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黄晓妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -431,6 +395,74 @@
   </si>
   <si>
     <t>驱动C#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文世童</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成测试设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbMigrate 导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C++</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文世童</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何荣德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/何荣德</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,7 +470,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,13 +506,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,13 +549,6 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -621,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -632,33 +650,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,11 +969,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -969,520 +988,500 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>45</v>
+      <c r="F2" s="7"/>
+      <c r="G2" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="25"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="25"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27" hidden="1">
+      <c r="A4" s="23"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>35</v>
+      <c r="C4" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="54">
-      <c r="A5" s="25"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54" hidden="1">
+      <c r="A5" s="23"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="108" hidden="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="108">
-      <c r="A8" s="25"/>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>51</v>
+      <c r="F8" s="7"/>
+      <c r="G8" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="25"/>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
+      <c r="A9" s="23"/>
+      <c r="B9" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="25"/>
-      <c r="B10" s="18" t="s">
-        <v>10</v>
+        <v>67</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A10" s="23"/>
+      <c r="B10" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
+      <c r="A11" s="23"/>
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="25"/>
-      <c r="B12" s="2" t="s">
+      <c r="F11" s="4"/>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="25"/>
-      <c r="B13" s="18" t="s">
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
+      <c r="A13" s="23"/>
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="25"/>
+        <v>32</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1">
+      <c r="A14" s="23"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>16</v>
+      <c r="C14" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>51</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="25"/>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A15" s="23"/>
+      <c r="B15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>33</v>
+        <v>57</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="25"/>
-      <c r="B16" s="18" t="s">
-        <v>24</v>
+      <c r="A16" s="23"/>
+      <c r="B16" s="16" t="s">
+        <v>21</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="25"/>
-      <c r="B17" s="18" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1">
+      <c r="A17" s="23"/>
+      <c r="B17" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
         <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="F17" s="4"/>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26" t="s">
-        <v>67</v>
+      <c r="A18" s="23"/>
+      <c r="B18" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26" t="s">
-        <v>68</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
+      <c r="A19" s="23"/>
+      <c r="B19" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="25"/>
-      <c r="B20" s="18" t="s">
-        <v>72</v>
+        <v>61</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" hidden="1">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>33</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="25"/>
-      <c r="B21" s="18" t="s">
-        <v>71</v>
+      <c r="A21" s="23"/>
+      <c r="B21" s="19" t="s">
+        <v>52</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="25"/>
-      <c r="B22" s="22" t="s">
-        <v>59</v>
+      <c r="F21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1">
+      <c r="A22" s="23"/>
+      <c r="B22" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="25"/>
-      <c r="B23" s="18" t="s">
-        <v>21</v>
+      <c r="F22" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F23" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="25"/>
-      <c r="B24" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" t="s">
-        <v>39</v>
-      </c>
       <c r="E24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="25"/>
-      <c r="B25" s="7" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
+      <c r="A26" s="23"/>
+      <c r="B26" s="17" t="s">
         <v>25</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="F25" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="25"/>
-      <c r="B26" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="25"/>
-      <c r="B27" s="11" t="s">
+      <c r="F26" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
+      <c r="A27" s="23"/>
+      <c r="B27" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
+      <c r="B28" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="25"/>
-      <c r="B28" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="25"/>
-      <c r="B29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="B30" s="23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" t="s">
-        <v>63</v>
+      <c r="B30" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G30">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="高"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A2:A29"/>
+    <mergeCell ref="A2:A27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,13 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>story</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story用例目录，根据不同story划分子目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -209,18 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成测试设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.17完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.16完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>元数据操作：
 domain,
 CS(create,drop,list),
@@ -229,30 +213,6 @@
   </si>
   <si>
     <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.10完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.12完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.15完成测试用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.14完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.19完成测试方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划6.11完成测试用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -414,18 +374,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>完成测试设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>梁雪望</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdbMigrate 导入导出工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>spark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -463,6 +415,39 @@
   </si>
   <si>
     <t>黄晓妮/何荣德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbimprt/sdbimprt-jdbc/sdbexprt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story目录/子目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>另sdbMigrate：不同集群间的数据迁移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未测试部分：
+sdbexprt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +540,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -580,8 +565,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -608,30 +599,21 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -639,11 +621,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -652,7 +631,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -661,20 +639,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -970,507 +962,588 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="40.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="30.75" customWidth="1"/>
+    <col min="3" max="3" width="23.75" customWidth="1"/>
+    <col min="4" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="24"/>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="40.5" hidden="1">
+      <c r="A4" s="24"/>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="54" hidden="1">
+      <c r="A5" s="24"/>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A6" s="24"/>
+      <c r="B6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="121.5" hidden="1">
+      <c r="A7" s="24"/>
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" hidden="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="27">
+      <c r="A9" s="24"/>
+      <c r="B9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1">
-      <c r="A2" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="24.75" customHeight="1">
+      <c r="A10" s="24"/>
+      <c r="B10" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="26">
+        <v>42653</v>
+      </c>
+      <c r="H10" s="26">
+        <v>42657</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" hidden="1">
+      <c r="A11" s="24"/>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" hidden="1">
+      <c r="A12" s="24"/>
+      <c r="B12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" hidden="1">
+      <c r="A13" s="24"/>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" hidden="1">
+      <c r="A14" s="24"/>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="24"/>
+      <c r="B15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="24"/>
+      <c r="B16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" hidden="1">
+      <c r="A17" s="24"/>
+      <c r="B17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="24"/>
+      <c r="B18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" hidden="1">
+      <c r="A19" s="24"/>
+      <c r="B19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
+      <c r="A20" s="24"/>
+      <c r="B20" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="24"/>
+      <c r="B21" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
+      <c r="A22" s="24"/>
+      <c r="B22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="23"/>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" hidden="1">
+      <c r="A23" s="24"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" hidden="1">
+      <c r="A24" s="24"/>
+      <c r="B24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="24"/>
+      <c r="B25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" hidden="1">
+      <c r="A26" s="24"/>
+      <c r="B26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" hidden="1">
+      <c r="A27" s="24"/>
+      <c r="B27" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" hidden="1">
+      <c r="B28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27" hidden="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="54" hidden="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="108" hidden="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" hidden="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="23"/>
-      <c r="B9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" hidden="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" hidden="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" hidden="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="23"/>
-      <c r="B15" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="23"/>
-      <c r="B16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="23"/>
-      <c r="B18" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" hidden="1">
-      <c r="A19" s="23"/>
-      <c r="B19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" hidden="1">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="23"/>
-      <c r="B21" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1">
-      <c r="A22" s="23"/>
-      <c r="B22" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1">
-      <c r="A23" s="23"/>
-      <c r="B23" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="23"/>
-      <c r="B25" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1">
-      <c r="A26" s="23"/>
-      <c r="B26" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="23"/>
-      <c r="B27" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1">
-      <c r="B28" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="26">
+        <v>42658</v>
+      </c>
+      <c r="H30" s="26">
+        <v>42688</v>
+      </c>
+      <c r="I30" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G30">

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,10 @@
   <si>
     <t>未测试部分：
 sdbexprt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spark连接器问题单修改后再投入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -621,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -657,22 +661,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -684,7 +757,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -978,33 +1051,33 @@
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" hidden="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1025,7 +1098,7 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="24"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1041,12 +1114,16 @@
       <c r="F3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="24">
+        <v>42643</v>
+      </c>
+      <c r="H3" s="24">
+        <v>42673</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="40.5" hidden="1">
-      <c r="A4" s="24"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1064,8 +1141,8 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="54" hidden="1">
-      <c r="A5" s="24"/>
+    <row r="5" spans="1:9" ht="67.5" hidden="1">
+      <c r="A5" s="26"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1084,7 +1161,7 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A6" s="24"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
@@ -1100,12 +1177,16 @@
       <c r="F6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="24">
+        <v>42621</v>
+      </c>
+      <c r="H6" s="24">
+        <v>42626</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="121.5" hidden="1">
-      <c r="A7" s="24"/>
+    <row r="7" spans="1:9" ht="162" hidden="1">
+      <c r="A7" s="26"/>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
@@ -1124,7 +1205,7 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" hidden="1">
-      <c r="A8" s="24"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1141,7 +1222,7 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="27">
-      <c r="A9" s="24"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
@@ -1157,12 +1238,16 @@
       <c r="F9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="G9" s="27">
+        <v>42623</v>
+      </c>
+      <c r="H9" s="27">
+        <v>42633</v>
+      </c>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A10" s="24"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="19" t="s">
         <v>70</v>
       </c>
@@ -1178,10 +1263,10 @@
       <c r="F10" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="24">
         <v>42653</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="24">
         <v>42657</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1189,7 +1274,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" hidden="1">
-      <c r="A11" s="24"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,7 +1293,7 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" hidden="1">
-      <c r="A12" s="24"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
@@ -1223,7 +1308,7 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" hidden="1">
-      <c r="A13" s="24"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1242,7 +1327,7 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" hidden="1">
-      <c r="A14" s="24"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1261,7 +1346,7 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="24"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="13" t="s">
         <v>64</v>
       </c>
@@ -1275,12 +1360,16 @@
       <c r="F15" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="G15" s="24">
+        <v>42636</v>
+      </c>
+      <c r="H15" s="24">
+        <v>42673</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="24"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="13" t="s">
         <v>20</v>
       </c>
@@ -1294,12 +1383,16 @@
       <c r="F16" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="G16" s="24">
+        <v>42623</v>
+      </c>
+      <c r="H16" s="24">
+        <v>42673</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" hidden="1">
-      <c r="A17" s="24"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="17" t="s">
         <v>48</v>
       </c>
@@ -1316,7 +1409,7 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="24"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1330,12 +1423,16 @@
       <c r="F18" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="G18" s="24">
+        <v>42613</v>
+      </c>
+      <c r="H18" s="24">
+        <v>42643</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="24"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="13" t="s">
         <v>53</v>
       </c>
@@ -1354,7 +1451,7 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="24"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="18" t="s">
         <v>52</v>
       </c>
@@ -1371,7 +1468,7 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="24"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="16" t="s">
         <v>42</v>
       </c>
@@ -1385,12 +1482,16 @@
       <c r="F21" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="G21" s="24">
+        <v>42658</v>
+      </c>
+      <c r="H21" s="24">
+        <v>42689</v>
+      </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="24"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="13" t="s">
         <v>18</v>
       </c>
@@ -1409,7 +1510,7 @@
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="24"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="13" t="s">
         <v>19</v>
       </c>
@@ -1428,7 +1529,7 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="24"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1445,7 +1546,7 @@
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="24"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1459,12 +1560,16 @@
       <c r="F25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="G25" s="24">
+        <v>42613</v>
+      </c>
+      <c r="H25" s="24">
+        <v>42615</v>
+      </c>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="24"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="14" t="s">
         <v>24</v>
       </c>
@@ -1481,7 +1586,7 @@
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" hidden="1">
-      <c r="A27" s="24"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="15" t="s">
         <v>43</v>
       </c>
@@ -1519,9 +1624,15 @@
       <c r="F29" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="G29" s="24">
+        <v>42643</v>
+      </c>
+      <c r="H29" s="24">
+        <v>42673</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="16" t="s">
@@ -1537,10 +1648,10 @@
       <c r="F30" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="24">
         <v>42658</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="24">
         <v>42688</v>
       </c>
       <c r="I30" s="1"/>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -665,13 +665,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1077,7 +1077,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" hidden="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1098,7 +1098,7 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="26"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1123,7 +1123,7 @@
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="40.5" hidden="1">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1142,7 +1142,7 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="67.5" hidden="1">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
@@ -1178,15 +1178,15 @@
         <v>26</v>
       </c>
       <c r="G6" s="24">
-        <v>42621</v>
+        <v>42625</v>
       </c>
       <c r="H6" s="24">
-        <v>42626</v>
+        <v>42627</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="162" hidden="1">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
@@ -1205,7 +1205,7 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" hidden="1">
-      <c r="A8" s="26"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,7 +1222,7 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="27">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
@@ -1238,16 +1238,16 @@
       <c r="F9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="25">
         <v>42623</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="25">
         <v>42633</v>
       </c>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="19" t="s">
         <v>70</v>
       </c>
@@ -1274,7 +1274,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" hidden="1">
-      <c r="A11" s="26"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1293,7 +1293,7 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" hidden="1">
-      <c r="A12" s="26"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
@@ -1308,7 +1308,7 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" hidden="1">
-      <c r="A13" s="26"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1327,7 +1327,7 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" hidden="1">
-      <c r="A14" s="26"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="26"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="13" t="s">
         <v>64</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="26"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="13" t="s">
         <v>20</v>
       </c>
@@ -1392,7 +1392,7 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" hidden="1">
-      <c r="A17" s="26"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="17" t="s">
         <v>48</v>
       </c>
@@ -1409,7 +1409,7 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="26"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1432,7 +1432,7 @@
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="26"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="13" t="s">
         <v>53</v>
       </c>
@@ -1451,7 +1451,7 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="26"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="18" t="s">
         <v>52</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="26"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="16" t="s">
         <v>42</v>
       </c>
@@ -1491,7 +1491,7 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="26"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="13" t="s">
         <v>18</v>
       </c>
@@ -1510,7 +1510,7 @@
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="26"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="13" t="s">
         <v>19</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="26"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="26"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="26"/>
+      <c r="A26" s="27"/>
       <c r="B26" s="14" t="s">
         <v>24</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" hidden="1">
-      <c r="A27" s="26"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="15" t="s">
         <v>43</v>
       </c>

--- a/internal_doc/05.测试设计/用例分类.xlsx
+++ b/internal_doc/05.测试设计/用例分类.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="72">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,9 +180,6 @@
   </si>
   <si>
     <t>王文净</t>
-  </si>
-  <si>
-    <t>龙阳</t>
   </si>
   <si>
     <t>主要责任人</t>
@@ -334,10 +331,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Java Script</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>驱动JAVA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -382,10 +375,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -403,18 +392,6 @@
   </si>
   <si>
     <t>王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文世童</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何荣德</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮/何荣德</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -678,74 +655,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -757,7 +666,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1034,8 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="30.75" customWidth="1"/>
@@ -1052,31 +960,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>35</v>
       </c>
       <c r="F1" s="23" t="s">
         <v>25</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" hidden="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1084,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>30</v>
@@ -1106,13 +1014,13 @@
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3" s="24">
         <v>42643</v>
@@ -1122,7 +1030,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="40.5" hidden="1">
+    <row r="4" spans="1:9" ht="40.5">
       <c r="A4" s="27"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -1141,19 +1049,19 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="67.5" hidden="1">
+    <row r="5" spans="1:9" ht="67.5">
       <c r="A5" s="27"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
@@ -1169,10 +1077,10 @@
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>26</v>
@@ -1185,16 +1093,16 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="162" hidden="1">
+    <row r="7" spans="1:9" ht="162">
       <c r="A7" s="27"/>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>28</v>
@@ -1204,14 +1112,14 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9">
       <c r="A8" s="27"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>30</v>
@@ -1227,13 +1135,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>26</v>
@@ -1249,17 +1157,15 @@
     <row r="10" spans="1:9" ht="24.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="19" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>67</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="20" t="s">
         <v>26</v>
       </c>
@@ -1270,10 +1176,10 @@
         <v>42657</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" hidden="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="27"/>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -1292,7 +1198,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" hidden="1">
+    <row r="12" spans="1:9">
       <c r="A12" s="27"/>
       <c r="B12" s="18" t="s">
         <v>11</v>
@@ -1307,7 +1213,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" hidden="1">
+    <row r="13" spans="1:9">
       <c r="A13" s="27"/>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -1326,7 +1232,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9">
       <c r="A14" s="27"/>
       <c r="B14" s="1" t="s">
         <v>13</v>
@@ -1335,7 +1241,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>31</v>
@@ -1348,14 +1254,14 @@
     <row r="15" spans="1:9">
       <c r="A15" s="27"/>
       <c r="B15" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>26</v>
@@ -1375,13 +1281,13 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G16" s="24">
         <v>42623</v>
@@ -1391,281 +1297,252 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" hidden="1">
+    <row r="17" spans="1:9">
       <c r="A17" s="27"/>
       <c r="B17" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="24">
+        <v>42613</v>
+      </c>
+      <c r="H17" s="24">
+        <v>42643</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="27"/>
-      <c r="B18" s="17" t="s">
-        <v>49</v>
+      <c r="B18" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="27"/>
+      <c r="B19" s="18" t="s">
         <v>50</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="24">
-        <v>42613</v>
-      </c>
-      <c r="H18" s="24">
-        <v>42643</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="27"/>
-      <c r="B19" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>27</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F19" s="10"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" hidden="1">
+    <row r="20" spans="1:9">
       <c r="A20" s="27"/>
-      <c r="B20" s="18" t="s">
-        <v>52</v>
+      <c r="B20" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="24">
+        <v>42658</v>
+      </c>
+      <c r="H20" s="24">
+        <v>42689</v>
+      </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="27"/>
-      <c r="B21" s="16" t="s">
-        <v>42</v>
+      <c r="B21" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="24">
-        <v>42658</v>
-      </c>
-      <c r="H21" s="24">
-        <v>42689</v>
-      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" hidden="1">
+    <row r="22" spans="1:9">
       <c r="A22" s="27"/>
       <c r="B22" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="10" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" hidden="1">
+    <row r="23" spans="1:9">
       <c r="A23" s="27"/>
-      <c r="B23" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="1"/>
+      <c r="B23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="8"/>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" hidden="1">
+    <row r="24" spans="1:9">
       <c r="A24" s="27"/>
-      <c r="B24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="8"/>
+      <c r="B24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="D24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="24">
+        <v>42613</v>
+      </c>
+      <c r="H24" s="24">
+        <v>42615</v>
+      </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="27"/>
-      <c r="B25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="B25" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8"/>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="24">
-        <v>42613</v>
-      </c>
-      <c r="H25" s="24">
-        <v>42615</v>
-      </c>
+      <c r="F25" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" hidden="1">
+    <row r="26" spans="1:9">
       <c r="A26" s="27"/>
-      <c r="B26" s="14" t="s">
-        <v>24</v>
+      <c r="B26" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="11" t="s">
-        <v>27</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" hidden="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="15" t="s">
+    <row r="27" spans="1:9">
+      <c r="B27" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="8"/>
+      <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" hidden="1">
-      <c r="B28" s="16" t="s">
-        <v>44</v>
+    <row r="28" spans="1:9">
+      <c r="B28" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="24">
+        <v>42643</v>
+      </c>
+      <c r="H28" s="24">
+        <v>42673</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="B29" s="1" t="s">
-        <v>59</v>
+      <c r="B29" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="24">
-        <v>42643</v>
+        <v>42658</v>
       </c>
       <c r="H29" s="24">
-        <v>42673</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="B30" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="24">
-        <v>42658</v>
-      </c>
-      <c r="H30" s="24">
         <v>42688</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I29" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G30">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="高"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:G29">
+    <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A2:A27"/>
+    <mergeCell ref="A2:A26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
